--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494082.3609503417</v>
+        <v>494083</v>
       </c>
       <c r="R17" t="n">
-        <v>6865068.66194774</v>
+        <v>6865068</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,19 +2471,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,12 +2489,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Gabriella Johansson</t>
+          <t>Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gabriella Johansson</t>
+          <t>Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3079,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3116,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494103.8228979579</v>
+        <v>494104</v>
       </c>
       <c r="R23" t="n">
-        <v>6865202.877701303</v>
+        <v>6865203</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,19 +3139,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,12 +3157,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gabriella Johansson</t>
+          <t>Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gabriella Johansson</t>
+          <t>Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,11 +2415,6 @@
       </c>
       <c r="E17" t="n">
         <v>219790</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3069,7 +3064,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3083,11 +3078,6 @@
       </c>
       <c r="E23" t="n">
         <v>219790</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,6 +2415,11 @@
       </c>
       <c r="E17" t="n">
         <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3064,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3078,6 +3083,11 @@
       </c>
       <c r="E23" t="n">
         <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -2401,7 +2401,7 @@
         <v>106039417</v>
       </c>
       <c r="B17" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>106039416</v>
       </c>
       <c r="B23" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3506,6 +3506,118 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124956570</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>493894</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6865036</v>
+      </c>
+      <c r="S27" t="n">
+        <v>12</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -3511,7 +3511,7 @@
         <v>124956570</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 38535-2019 artfynd.xlsx
+++ b/artfynd/A 38535-2019 artfynd.xlsx
@@ -3513,11 +3513,6 @@
       <c r="B27" t="n">
         <v>56836</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>LC</t>
